--- a/data/4-reports/6_DOID_Matches_All.xlsx
+++ b/data/4-reports/6_DOID_Matches_All.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I214"/>
+  <dimension ref="A1:I215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7891,6 +7891,49 @@
       </c>
       <c r="H214" s="2" t="inlineStr"/>
       <c r="I214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>ARI:0001216</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Hashimoto's thyroiditis</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>DOID:7188</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>autoimmune thyroiditis</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>synonym</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>190297000</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
@@ -8023,6 +8066,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8034,7 +8078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15504,6 +15548,66 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>ARI:0001216</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Hashimoto's thyroiditis</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>DOID:7188</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>autoimmune thyroiditis</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>An autoimmune disease of endocrine system that involves inflammation located_in thyroid gland caused by the immune system reacting against its own tissues.</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Chronic Lymphocytic Thyroiditis; Hashimoto thyroiditis; Hashimoto's Disease; Hashimoto's syndrome; Hashimoto's thyroiditis; Lymphocytic Thyroiditis</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>SNOMEDCT_US_2025_09_01:190297000</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>MESH:D013967</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>NCI:C38766</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>UMLS_CUI:C0920350</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>ICD10CM:E06.3</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
@@ -15636,6 +15740,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
